--- a/Electronics/BOM.xlsx
+++ b/Electronics/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\DSpi 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{928EB7CA-9196-444D-B5D2-F414ACC8B6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D06133-088C-414A-8ABF-D40B9F9BA170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{6C9980FC-E369-47A3-97AE-CE2F8754E070}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
   <si>
     <t>Part</t>
   </si>
@@ -189,6 +189,24 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>SP-1605</t>
+  </si>
+  <si>
+    <t>Speakers x2</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com.au/en/products/detail/soberton-inc/SP-1605/3973691</t>
+  </si>
+  <si>
+    <t>Speaker wires</t>
+  </si>
+  <si>
+    <t>jst sur 2p 0.8mm 200mm</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005009264311917.html</t>
   </si>
 </sst>
 </file>
@@ -224,10 +242,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -597,7 +614,7 @@
       <c r="C2">
         <v>52.7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -611,7 +628,7 @@
       <c r="C3">
         <v>53.7</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -625,7 +642,7 @@
       <c r="C4">
         <v>276</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>47</v>
       </c>
     </row>
@@ -639,7 +656,7 @@
       <c r="C5">
         <v>9</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -830,8 +847,36 @@
         <v>45</v>
       </c>
     </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>55</v>
+      </c>
+    </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="2"/>
+      <c r="B22" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
